--- a/naver-place-crawler/results_health/부천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부천_헬스장.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>울프짐24 헬스 PT 부천중동점</t>
+          <t>루크짐 약대점 24시 연중무휴 헬스장 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wolfgym24@naver.com</t>
+          <t>sensegym_hs_jongbeen@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1385-9684</t>
+          <t>0507-1447-5541</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 219 405호</t>
+          <t>경기 부천시 원미구 중동로 370 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wolfgym24_1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5y404</t>
+          <t>https://talk.naver.com/ct/wc3sbuq</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>935</v>
+        <v>591</v>
       </c>
       <c r="Q2" t="n">
-        <v>2878</v>
+        <v>146</v>
       </c>
       <c r="R2" t="n">
-        <v>3813</v>
+        <v>737</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1363211482</t>
+          <t>2002148114</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363211482</t>
+          <t>https://m.place.naver.com/place/2002148114</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,35 +662,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>쏘마휘트니스 부천상동점</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>휘트니스피플 우먼 신중동점</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1340-3115</t>
+          <t>032-324-3912</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부일로 223</t>
+          <t>경기 부천시 원미구 중동로262번길 32 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.gymss.co.kr/GymSubscribe</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a8bu</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>5372</v>
+        <v>1429</v>
       </c>
       <c r="Q3" t="n">
-        <v>2855</v>
+        <v>3009</v>
       </c>
       <c r="R3" t="n">
-        <v>8227</v>
+        <v>4438</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1370160364</t>
+          <t>1463533676</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370160364</t>
+          <t>https://m.place.naver.com/place/1463533676</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스탠다드 피트니스 헬스 PT 부천상동점</t>
+          <t>쏘마휘트니스 부천상동점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>standard_songnae@naver.com</t>
+          <t>ruwkxkd@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1402-3452</t>
+          <t>0507-1340-3115</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
+          <t>경기 부천시 원미구 부일로 223</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standard_songnae</t>
+          <t>https://www.gymss.co.kr/GymSubscribe</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,19 +797,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ijgb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>960</v>
+        <v>5386</v>
       </c>
       <c r="Q4" t="n">
-        <v>1930</v>
+        <v>2924</v>
       </c>
       <c r="R4" t="n">
-        <v>2890</v>
+        <v>8310</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1330383759</t>
+          <t>1370160364</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330383759</t>
+          <t>https://m.place.naver.com/place/1370160364</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -850,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>빌리프짐 헬스&amp;PT 상동점</t>
+          <t>휘트니스피플 우먼 상동역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>beliefgym5@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1368-6967</t>
+          <t>032-324-3913</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
+          <t>경기 부천시 원미구 길주로 86 2층 203, 204, 205호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -897,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49j5b</t>
+          <t>https://talk.naver.com/ct/w5xvys</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1429</v>
+        <v>1728</v>
       </c>
       <c r="Q5" t="n">
-        <v>2298</v>
+        <v>2645</v>
       </c>
       <c r="R5" t="n">
-        <v>3727</v>
+        <v>4373</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1793743090</t>
+          <t>1877112504</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1793743090</t>
+          <t>https://m.place.naver.com/place/1877112504</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -948,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>휘트니스 라운지</t>
+          <t>디에이트짐 헬스 PT 부천상동2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fitnesslounge01@naver.com</t>
+          <t>boyoung2da@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1369-7029</t>
+          <t>0507-1441-2997</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 중동로248번길 52 네이버시티 8층</t>
+          <t>경기 부천시 원미구 상동로 81 801호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitnesslounge01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,7 +984,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -995,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40kmm</t>
+          <t>https://talk.naver.com/ct/w40sp5</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1009,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1115</v>
+        <v>2319</v>
       </c>
       <c r="Q6" t="n">
-        <v>1542</v>
+        <v>3624</v>
       </c>
       <c r="R6" t="n">
-        <v>2657</v>
+        <v>5943</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1224652257</t>
+          <t>1073116020</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1224652257</t>
+          <t>https://m.place.naver.com/place/1073116020</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1046,39 +1050,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>청년피티 상동점</t>
+          <t>스포애니 부천심곡점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cnpt1212@naver.com</t>
+          <t>42_spoany@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1407-1212</t>
+          <t>0507-1381-9618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 송내대로265번길 17</t>
+          <t>경기 부천시 소사구 경인로 175</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cnptoffical.qshop.ai/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1093,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tdfl</t>
+          <t>https://talk.naver.com/ct/w5yomq</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>535</v>
+        <v>696</v>
       </c>
       <c r="Q7" t="n">
-        <v>1473</v>
+        <v>1965</v>
       </c>
       <c r="R7" t="n">
-        <v>2008</v>
+        <v>2661</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37578803</t>
+          <t>420802340</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37578803</t>
+          <t>https://m.place.naver.com/place/420802340</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>청년피티 중동점</t>
+          <t>다니엘짐 부천상동점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cnpt_jd@naver.com</t>
+          <t>danielgym1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1349-1213</t>
+          <t>0507-1458-9683</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부흥로315번길 58</t>
+          <t>경기 부천시 원미구 길주로 137</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cnpt_jd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,12 +1180,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1191,12 +1195,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47rdn</t>
+          <t>https://talk.naver.com/ct/w4bgn0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>411</v>
+        <v>1116</v>
       </c>
       <c r="Q8" t="n">
-        <v>345</v>
+        <v>285</v>
       </c>
       <c r="R8" t="n">
-        <v>756</v>
+        <v>1401</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1576345626</t>
+          <t>1967595040</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576345626</t>
+          <t>https://m.place.naver.com/place/1967595040</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1268,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ehehehans</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,12 +1278,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Q9" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="R9" t="n">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1328,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1366,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,12 +1376,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="Q10" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R10" t="n">
-        <v>1491</v>
+        <v>1510</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1426,41 +1430,41 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디플래너 PT</t>
+          <t>바디채널 짐그라운드 상동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyplanner2@naver.com</t>
+          <t>bodych_55@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1353-4708</t>
+          <t>0507-1358-8868</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 오정구 여월로 72</t>
+          <t>경기 부천시 원미구 상동로 83</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplanner2</t>
+          <t>https://blog.naver.com/bodych_55</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46rbk</t>
+          <t>https://talk.naver.com/ct/w4s18q</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>68</v>
+        <v>549</v>
       </c>
       <c r="Q11" t="n">
-        <v>96</v>
+        <v>3704</v>
       </c>
       <c r="R11" t="n">
-        <v>164</v>
+        <v>4253</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1504406955</t>
+          <t>36943245</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1504406955</t>
+          <t>https://m.place.naver.com/place/36943245</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부천_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 신중동점</t>
+          <t>YS휘트니스 송내점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>ysfitness2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>032-324-3912</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 중동로262번길 32 3층</t>
+          <t>경기도 부천시 원미구 상일로 100 7층 701호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ysfitness2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +592,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4a8bu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1428</v>
+        <v>212</v>
       </c>
       <c r="Q2" t="n">
-        <v>3037</v>
+        <v>98</v>
       </c>
       <c r="R2" t="n">
-        <v>4465</v>
+        <v>310</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1463533676</t>
+          <t>2091889709</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463533676</t>
+          <t>https://m.place.naver.com/place/2091889709</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -662,29 +654,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>디에이트짐 헬스 PT 부천상동2호점</t>
+          <t>휘트니스피플 우먼 신중동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>boyoung2da@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1441-2997</t>
+          <t>032-324-3912</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 81 801호</t>
+          <t>경기도 부천시 원미구 중동로262번길 32 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +686,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40sp5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2342</v>
+        <v>1428</v>
       </c>
       <c r="Q3" t="n">
-        <v>3626</v>
+        <v>3037</v>
       </c>
       <c r="R3" t="n">
-        <v>5968</v>
+        <v>4465</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1073116020</t>
+          <t>1463533676</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073116020</t>
+          <t>https://m.place.naver.com/place/1463533676</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,29 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포애니 부천심곡점</t>
+          <t>바디채널 짐그라운드 상동점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>42_spoany@naver.com</t>
+          <t>bodych_55@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1381-9618</t>
+          <t>0507-1358-8868</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 부천시 소사구 경인로 175</t>
+          <t>경기도 부천시 원미구 상동로 83</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bodych_55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,24 +780,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yomq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>703</v>
+        <v>552</v>
       </c>
       <c r="Q4" t="n">
-        <v>1972</v>
+        <v>3706</v>
       </c>
       <c r="R4" t="n">
-        <v>2675</v>
+        <v>4258</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>420802340</t>
+          <t>36943245</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/420802340</t>
+          <t>https://m.place.naver.com/place/36943245</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -858,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 신중동점</t>
+          <t>비앤알휘트니스 헬스,골프,스쿼시,PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany36s@naver.com</t>
+          <t>dhqueen@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1415-5517</t>
+          <t>0507-1305-6989</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 신흥로 169 미림프라자 5층</t>
+          <t>경기도 부천시 원미구 조마루로 387 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dhqueen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +874,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -915,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2176</v>
+        <v>424</v>
       </c>
       <c r="Q5" t="n">
-        <v>2472</v>
+        <v>119</v>
       </c>
       <c r="R5" t="n">
-        <v>4648</v>
+        <v>543</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37870631</t>
+          <t>13452681</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37870631</t>
+          <t>https://m.place.naver.com/place/13452681</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -952,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 부천역점</t>
+          <t>스탠다드 피트니스 헬스 PT 부천상동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany71@naver.com</t>
+          <t>standard_songnae@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>032-663-9618</t>
+          <t>0507-1402-3452</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로 47</t>
+          <t>경기도 부천시 원미구 부일로191번길 26 우신프라자 5층 스탠다드 피트니스 부천상동점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/standard_songnae</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,24 +968,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yrx8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>659</v>
+        <v>978</v>
       </c>
       <c r="Q6" t="n">
-        <v>1491</v>
+        <v>1966</v>
       </c>
       <c r="R6" t="n">
-        <v>2150</v>
+        <v>2944</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1759397301</t>
+          <t>1330383759</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759397301</t>
+          <t>https://m.place.naver.com/place/1330383759</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1050,39 +1030,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>디엠짐 헬스장</t>
+          <t>모티빅 피트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ehehehans@naver.com</t>
+          <t>hjae303014@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-230-9200</t>
+          <t>0507-1335-5229</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로 120</t>
+          <t>경기도 부천시 원미구 부흥로303번길 36 701호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://map.naver.com/p/entry/place/1350157996?c=15.00,0,0,0,dh&amp;placePath=/home</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1092,14 +1072,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc9e55</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>525</v>
+        <v>313</v>
       </c>
       <c r="Q7" t="n">
-        <v>526</v>
+        <v>89</v>
       </c>
       <c r="R7" t="n">
-        <v>1051</v>
+        <v>402</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1830766808</t>
+          <t>1670860011</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1830766808</t>
+          <t>https://m.place.naver.com/place/1670860011</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 부천역점</t>
+          <t>짐클래식</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>gymclassic@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-613-3912</t>
+          <t>032-345-8301</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 부천로29번길 7 2층</t>
+          <t>경기도 부천시 소사구 경인로 522 위드프러스타워 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/gymclassic</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1190,14 +1166,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42rk8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1225</v>
+        <v>152</v>
       </c>
       <c r="Q8" t="n">
-        <v>293</v>
+        <v>42</v>
       </c>
       <c r="R8" t="n">
-        <v>1518</v>
+        <v>194</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1701536337</t>
+          <t>1341032754</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701536337</t>
+          <t>https://m.place.naver.com/place/1341032754</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1246,25 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YS휘트니스 송내점</t>
+          <t>빌리프짐 헬스&amp;PT 상동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ysfitness2@naver.com</t>
+          <t>beliefgym5@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1368-6967</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상일로 100 7층 701호</t>
+          <t>경기도 부천시 원미구 길주로 105 8층 빌리프짐 상동점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/BELIEFGYM_SANGDONG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,7 +1250,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1284,14 +1260,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42z53</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>212</v>
+        <v>1446</v>
       </c>
       <c r="Q9" t="n">
-        <v>97</v>
+        <v>2267</v>
       </c>
       <c r="R9" t="n">
-        <v>309</v>
+        <v>3713</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2091889709</t>
+          <t>1793743090</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2091889709</t>
+          <t>https://m.place.naver.com/place/1793743090</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스&amp;PT&amp;GX&amp;필라 상동역점</t>
+          <t>바디슈트짐 헬스&amp;PT 옥길점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>halogym1@naver.com</t>
+          <t>jdndjdjcicmdm@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1387-9634</t>
+          <t>0507-1390-8609</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 부천시 원미구 상동로 87 901호, 903호</t>
+          <t>경기도 부천시 소사구 옥길로 129 6층, 7층 바디슈트</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jdndjdjcicmdm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,27 +1344,23 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5pi0u2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2160</v>
+        <v>346</v>
       </c>
       <c r="Q10" t="n">
-        <v>736</v>
+        <v>358</v>
       </c>
       <c r="R10" t="n">
-        <v>2896</v>
+        <v>704</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,51 +1384,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1739130426</t>
+          <t>1555801248</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1739130426</t>
+          <t>https://m.place.naver.com/place/1555801248</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디플래너 PT</t>
+          <t>인싸짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyplanner2@naver.com</t>
+          <t>inssagym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1353-4708</t>
+          <t>0507-1351-3818</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 부천시 오정구 여월로 72</t>
+          <t>경기도 부천시 오정구 역곡로 482 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/inssagym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,24 +1438,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46rbk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>68</v>
+        <v>971</v>
       </c>
       <c r="Q11" t="n">
-        <v>97</v>
+        <v>1257</v>
       </c>
       <c r="R11" t="n">
-        <v>165</v>
+        <v>2228</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1478,8627 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1504406955</t>
+          <t>1198976988</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1504406955</t>
+          <t>https://m.place.naver.com/place/1198976988</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>여성전용 피트니스 지금 헬스&amp;PT&amp;플라잉요가&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fbwodud94@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1470-1980</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 소사로 754</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://litt.ly/fitness_jiguem</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>304</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>260</v>
+      </c>
+      <c r="R12" t="n">
+        <v>564</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1778409801</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1778409801</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>아지트짐</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>azitgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1364-1857</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인로392번길 46 지하1층 아지트짐</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/azitgym</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>596</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>178</v>
+      </c>
+      <c r="R13" t="n">
+        <v>774</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1759467399</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1759467399</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>청년피티 상동점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cnpt1212@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1407-1212</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 송내대로265번길 17</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://cnptoffical.qshop.ai/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>538</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1297</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1835</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>37578803</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37578803</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>리버스짐 부천점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rebirthgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1329-6425</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 158</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rebirthgym</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>324</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>145</v>
+      </c>
+      <c r="R15" t="n">
+        <v>469</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1168837876</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1168837876</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>에너지플러스짐</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>kimwhijong@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 4</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>19251276</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19251276</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 부천점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1312-6406</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 11 12층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=48</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1727</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>169</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1896</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1977386549</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1977386549</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>F45 신중동</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>f45sinjungdong@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 신흥로 223 신중동역 랜드마크 푸르지오시티 지하 1층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45_training_sinjungdong/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>106</v>
+      </c>
+      <c r="R18" t="n">
+        <v>193</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1219222510</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1219222510</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>스포애니 부천역점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>spoany71@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>032-663-9618</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 47</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany71</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>660</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1491</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2151</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1759397301</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1759397301</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>안녕휘트니스 원미점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>hi_bye52@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1385-5069</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 103 2층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hi_bye52</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>369</v>
+      </c>
+      <c r="R20" t="n">
+        <v>508</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1385540538</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1385540538</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>짐케어 부천 상동역점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>kappy0318@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1400-2747</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 80 로얄타워 6층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kappy0318</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>690</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>783</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1473</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1378907322</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1378907322</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>어반짐 고강점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>mona_p@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1430-0880</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 역곡로 488 3층/5층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/urbangym_01?igsh=MXZ4djh4dmpkenplag==</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1196</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>340</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1536</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1623921865</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1623921865</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 부천역점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>032-613-3912</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로29번길 7 2층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fpeoplew1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1226</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>293</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1519</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1701536337</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1701536337</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>스포짐 부천점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>spogym24@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1349-6228</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 조마루로385번길 92 부천테크노밸리 B1층 129호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_mwyFxj</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>562</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>342</v>
+      </c>
+      <c r="R24" t="n">
+        <v>904</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1755237138</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1755237138</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>070-4587-4427</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 원미동</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1414033243</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1414033243</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>안녕휘트니스 도당점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jsh_3963@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1365-5069</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 삼작로 278</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jsh_3963</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>292</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>774</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1066</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1690559808</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1690559808</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>메디핏짐 부천대점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>medifitgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1333-9110</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 장말로 351 2층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/medifitgym</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2070020560</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2070020560</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>청년헬스장 소사점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>cn_sosa@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1406-3733</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 소사로247번길 19</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://cnptoffical.qshop.ai/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>825</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>330</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1155</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1364187974</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1364187974</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>자마이카피트니스 앤 스파 부천점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jfk012012@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1326-2994</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 옥산로 7</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jamaica_bucheon?igsh=MWIyaWV4cW8xeWc3Zw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>602</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>647</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1249</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1326717825</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1326717825</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>한조바디짐 헬스&amp;pt 부천본점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>hanjo63433@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1423-6343</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인로 110-1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@user-pc6bi6nu7w?feature=shared</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>196</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>307</v>
+      </c>
+      <c r="R30" t="n">
+        <v>503</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1375235921</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1375235921</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>온더짐 헬스&amp;PT 원종역점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>onthegym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1442-0750</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 소사로 750 토수프라자 3층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/13/bizes/963812?theme=place&amp;entry=pll&amp;area=pll&amp;c=15.00,0,0,3,dh</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1165</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>334</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1499</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1276329333</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1276329333</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>디에이트짐 헬스 PT 부천상동2호점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>boyoung2da@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1441-2997</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 상동로 81 801호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/boyoung2da/224238169312</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>2343</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3626</v>
+      </c>
+      <c r="R32" t="n">
+        <v>5969</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1073116020</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1073116020</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>프리원핏 역곡점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>red_pomme@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>freewantfit.yeokgok@gmail.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1422-9993</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인로 482 지하1층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/10/bizes/1051130</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>13</v>
+      </c>
+      <c r="R33" t="n">
+        <v>80</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1016060966</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1016060966</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>울프짐24 헬스 PT 부천중동점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>wolfgym24@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1385-9684</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 219 405호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wolfgym24_1</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>951</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2946</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3897</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1363211482</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1363211482</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>세이브피트니스 범박점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>savefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1314-1799</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 범안로 117 B1층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/savefitness_beombak</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1426</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>458</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1884</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1758737148</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1758737148</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>힙트니스 신중동점 24시 헬스PT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>hiptness_@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1384-3219</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 280</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hiptness/</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1596</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2114</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3710</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1966410618</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1966410618</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 상동역점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>032-324-3913</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 86 2층 203, 204, 205호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitnesspeople_sangdong?igsh=MWg4azh4cHpseHkxbQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>1735</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2672</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4407</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1877112504</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1877112504</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>어스짐 헬스&amp;PT 원종점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>usgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1377-0541</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 원종로 56 4F,5F</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/usgym</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>482</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>648</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1130</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1821472542</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1821472542</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>고다짐 신중동점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>godagym4@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>032-721-5467</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 중동로254번길 41 201, 202호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/godagym4</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>828</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1151</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1599382714</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1599382714</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>울트라짐 중동역점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>point_01_@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1476-7100</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 중동로 48 대우프라자 9층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/point_01_</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>353</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>368</v>
+      </c>
+      <c r="R40" t="n">
+        <v>721</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1998539021</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1998539021</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>케이브짐 헬스 PT 연중무휴</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>cavegym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1392-1553</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 소향로 246 7층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xjgyan</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>2097</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1758</v>
+      </c>
+      <c r="R41" t="n">
+        <v>3855</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1634815946</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1634815946</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>스포애니 역곡역점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>spoany95_@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1397-9618</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인로 527</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTEy</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>379</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>307</v>
+      </c>
+      <c r="R42" t="n">
+        <v>686</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1758668626</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1758668626</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>짐토스24 도당점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gymtos_dd@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1317-8372</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 성곡로 91 2층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymtos_dd</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>702</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>548</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1710771113</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1710771113</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>피타짐 부천역점 24시 헬스PT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kimt_company@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1484-0722</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 3-1</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Hvtlb/chat</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>444</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1748</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2192</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1593213362</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1593213362</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>은성스포츠센터</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>gksthfasd2@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1463-7854</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 수도로 202 은성프라자 4층 휘트니스</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gksthfasd2</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>607</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>79</v>
+      </c>
+      <c r="R45" t="n">
+        <v>686</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>13519865</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13519865</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>스포애니 부천신흥시장점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>spoany655@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1425-1138</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 중동로 406 서경빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany655</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>776</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>514</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1290</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>11783231</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11783231</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>헤일로짐24시 헬스&amp;PT&amp;GX&amp;필라 상동역점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>halogym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1387-9634</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 상동로 87 901호, 903호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/halogym1</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5pi0u2</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>2160</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>736</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2896</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1739130426</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1739130426</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>트라이던피트니스 심곡점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>trydonefitness2-@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1482-4503</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인로 190 3층 303, 303-1호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.trydonefitness.com/</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>457</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>348</v>
+      </c>
+      <c r="R48" t="n">
+        <v>805</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1868995575</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1868995575</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>바이퍼짐 헬스 PT 부천중동점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>tlsdlscjf95@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부흥로 262 4층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_PTJnn</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>201</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>67</v>
+      </c>
+      <c r="R49" t="n">
+        <v>268</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1019194618</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1019194618</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>스포애니 부천심곡점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>42_spoany@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1381-9618</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인로 175</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/42_spoany</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>703</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1973</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2676</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>420802340</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/420802340</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>루크짐 약대점 24시 연중무휴 헬스장 PT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sensegym_hs_jongbeen@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1447-5541</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 중동로 370 2층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lukgy_m24yd/</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>592</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>146</v>
+      </c>
+      <c r="R51" t="n">
+        <v>738</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2002148114</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002148114</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>라온바디핏</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>kwfmarin@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>032-655-6788</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 원미로97번길 31 대희빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kwfmarin</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>18</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1618126606</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1618126606</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>온더짐 부천시청역점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>onthegym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1486-1171</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 석천로 176 6층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/on_the_gym2</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>554</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>752</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1306</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1767525708</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1767525708</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>인싸짐 중동점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>donkey348@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1323-3818</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부흥로 203 세화빌딩 4층, 5층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/donkey348</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>1387</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1592</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2979</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1574519330</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1574519330</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>스포애니 신중동점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>spoany36s@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1415-5517</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 신흥로 169 미림프라자 5층</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany36s</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>2177</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2474</v>
+      </c>
+      <c r="R55" t="n">
+        <v>4651</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>37870631</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37870631</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>레인헬스 &amp; PT 부천원미점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>aum6485@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1461-8229</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로90번길 8 아송빌딩 8층 801호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aum6485</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>35</v>
+      </c>
+      <c r="R56" t="n">
+        <v>77</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1327891154</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1327891154</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>트라이던피트니스</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>trydonefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1379-4501</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인로 56 6층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.trydonefitness.com/</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>663</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1587</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2250</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1583276383</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1583276383</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>라인제작소 헬스&amp;PT 옥길점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>rheods1@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1416-8299</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 옥길로 110-19 ES타워 5층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/line_studio_5?igsh=Mzd2MXQ3ZDlyY2Ni&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>594</v>
+      </c>
+      <c r="R58" t="n">
+        <v>822</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1891562623</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1891562623</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>리버스휘트니스 소사본동점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>scvzxc123@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1464-5610</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 은성로 91 삼원상가</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/scvzxc123</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>641</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>309</v>
+      </c>
+      <c r="R59" t="n">
+        <v>950</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>19259267</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19259267</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>프라임짐 헬스 PT 부천 송내역점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>primegym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1430-2581</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로 202-13 1, 2층 프라임짐</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/primegym_songnae_pt</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1612</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1349</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2961</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1109750190</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1109750190</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>바디채널&amp;바레톤 역곡북부점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>bodychannel-s@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1355-4780</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로 753</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodychannel-s</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>564</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2019</v>
+      </c>
+      <c r="R61" t="n">
+        <v>2583</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1545705352</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1545705352</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>크로스핏슈팅스타 소사역점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>juj1470@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인옛로 42</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/shootingstarbc</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>61</v>
+      </c>
+      <c r="R62" t="n">
+        <v>67</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1298418120</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1298418120</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>메디컬짐 소사점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>medicalgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1396-1056</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 소삼로 20 지하1층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_vxmeHn</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>792</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1255</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2047</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1912036144</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1912036144</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>씨드짐휘트니스 24시 PT 부천신중동점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>seedgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1410-9681</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 중동로254번길 104 802호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seedgym</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>339</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2801</v>
+      </c>
+      <c r="R64" t="n">
+        <v>3140</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1095014062</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1095014062</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>505피트니스</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>505fitness_01@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1325-3219</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 183 지하1층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/505fitness_01</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>2413</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1417</v>
+      </c>
+      <c r="R65" t="n">
+        <v>3830</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>38530995</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38530995</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>크로스핏빅풋 중동점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>bigfoot_bucheon@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1333-7968</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부흥로315번길 37</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://litt.ly/crossfit_bigfoot</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>142</v>
+      </c>
+      <c r="R66" t="n">
+        <v>344</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1959607850</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1959607850</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>헬스보이짐&amp;필라걸&amp;골프인 부천점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>healthboygym57@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1349-9300</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 7 5층, 6층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_tVHQb</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>825</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>954</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1779</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1657097715</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1657097715</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>바디업휘트니스</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sky19120@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1473-6051</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 원미로 126 501,601호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sky19120</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>19</v>
+      </c>
+      <c r="R68" t="n">
+        <v>55</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1100626508</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1100626508</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>운동하는날 송내점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>fitnessday009@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1349-8296</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로199번길 56 3층 운동하는날 송내점</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessday009/222800120021</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>301</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>731</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1032</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1106457464</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1106457464</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>바디온짐 24시 헬스&amp;PT 부천점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>bodyongym@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 장말로 273 4층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgxeskj</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>55</v>
+      </c>
+      <c r="R70" t="n">
+        <v>90</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1628660011</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628660011</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>디엠짐 헬스장</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ehehehans@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>032-230-9200</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 120</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc9e55</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>525</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>526</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1051</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1830766808</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1830766808</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>센스짐24 춘의점 연중무휴 헬스장 PT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>an_dadasea@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1482-7951</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 231 세종빌딩 2층 센스짐24 춘의점</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://litt.ly/sensegym_cu</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vcw9</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>942</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>341</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1283</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1473760070</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1473760070</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>레인PT 원미시장점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>aum6485@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1489-0532</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 원미로97번길 21 2층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wy0p</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>29</v>
+      </c>
+      <c r="R73" t="n">
+        <v>74</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1949388244</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1949388244</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>아크짐 헬스&amp;PT 신중동점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>arkgymjd@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1323-9924</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 중동로 244 4층 401호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yzz4</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>263</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1183</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1446</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1696331031</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1696331031</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>쏘마휘트니스 부천상동점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ruwkxkd@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1340-3115</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로 223</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.gymss.co.kr/GymSubscribe</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>5393</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>2967</v>
+      </c>
+      <c r="R75" t="n">
+        <v>8360</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1370160364</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1370160364</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 원종점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1480-8025</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 소사로 772 6층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=59</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>801</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>37</v>
+      </c>
+      <c r="R76" t="n">
+        <v>838</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1668362068</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1668362068</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>크로스핏 복</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>kickboxs@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 32 지하1층</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>30</v>
+      </c>
+      <c r="R77" t="n">
+        <v>37</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1787295977</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1787295977</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>스포애니 상동점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>jes393030@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1421-7601</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로 293</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jes393030</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>688</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1671</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2359</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>36314848</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36314848</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>광성스포츠센터</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>rhkdtjrghkd@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1357-6668</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 옥산로138번길 30 지하1층</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5urkm</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>156</v>
+      </c>
+      <c r="R79" t="n">
+        <v>337</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>723406963</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/723406963</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>짐스토리피트니스</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>gymstoryfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1470-7913</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인로 511</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t4lw</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>358</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>506</v>
+      </c>
+      <c r="R80" t="n">
+        <v>864</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1455168047</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1455168047</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>짐고GYMGO</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>gymgo_@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>032-668-0023</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 성주로 224 3층 GYMGO</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bhrm</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>617</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>360</v>
+      </c>
+      <c r="R81" t="n">
+        <v>977</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1114186066</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1114186066</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>070-4595-4088</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 춘의동</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1382649357</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1382649357</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>그레이트짐</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>great-gym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1475-0514</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 소사로 124 3층 그레이트짐</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42415</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>253</v>
+      </c>
+      <c r="R83" t="n">
+        <v>342</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1444003797</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1444003797</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>리바이피트니스 헬스&amp;PT 부천시청점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>levifitone@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>OO@OO.com</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1483-7719</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 227 5층 501,502호 리바이 피트니스</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://levifitone.sixshop.site/</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxet6xi</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>152</v>
+      </c>
+      <c r="R84" t="n">
+        <v>327</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2037126482</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2037126482</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>휘트니스 라운지</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>fitnesslounge01@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1369-7029</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 중동로248번길 52 네이버시티 8층</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40kmm</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>1119</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1222</v>
+      </c>
+      <c r="R85" t="n">
+        <v>2341</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1224652257</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1224652257</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>목욕탕,사우나</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>벽계수스파옥길&amp;봄휘트니스</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>minnnndi@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>032-345-9117</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 옥길로 116 퀸즈파크 A동 9층 벽계수스파</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/byuk_gyesu?igsh=NjEzY3l5Zm4xejF3&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>2191</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>587</v>
+      </c>
+      <c r="R86" t="n">
+        <v>2778</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1084365162</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1084365162</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>바디채널&amp;히트35 역곡남부점</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>bodyyg@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1324-4779</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인로 505</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyyg</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>417</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1980</v>
+      </c>
+      <c r="R87" t="n">
+        <v>2397</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1856530360</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1856530360</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>바른PT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>bareunpt123@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1356-4513</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 원미로 97-1 302호</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>475</v>
+      </c>
+      <c r="R88" t="n">
+        <v>484</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>2006016240</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2006016240</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>VITO PT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>azaz0820@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1316-5404</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 원미로144번길 26 2층 일부</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>8</v>
+      </c>
+      <c r="R89" t="n">
+        <v>40</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1914552581</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1914552581</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>지엠짐 부천중동점</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>gmgym_1st@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1348-8822</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 191 금영프라자 2층 202호</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gmgym_1st/</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>308</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>778</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1086</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1868176633</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1868176633</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>부천역PT리얼짐pt샵</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>oecd1549@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1433-9688</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로 448 프리존빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/oecd1549</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>271</v>
+      </c>
+      <c r="R91" t="n">
+        <v>274</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>37092799</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37092799</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>메디어트 그룹운동&amp;1:1PT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>mediet2025@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1487-1261</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 81</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mediet2025/224064710210</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>365</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>258</v>
+      </c>
+      <c r="R92" t="n">
+        <v>623</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>35013539</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35013539</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>강핏피티스튜디오</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>kangfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1364-8977</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 송내대로 239 부천소풍터미널3층</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kangfit</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>17</v>
+      </c>
+      <c r="R93" t="n">
+        <v>26</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1529316295</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1529316295</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>머슬피치랩 신중동역점</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>bluemoon_v@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1353-4497</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 신흥로 230 201호</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>http://blog.naver.com/bluemoon_v</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>45</v>
+      </c>
+      <c r="R94" t="n">
+        <v>118</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1359422963</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1359422963</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>크로스핏 웨이브</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>crossfit_wave_@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1328-8844</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 석천로183번길 19 지층 비01호</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/crossfit_wave_</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>98</v>
+      </c>
+      <c r="R95" t="n">
+        <v>262</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1763437354</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1763437354</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>부천 요무브PT</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>nrgnam@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>godnam@hanmail.net</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>032-655-0888</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 신흥로56번길 30 2, 3, 4층</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@yomove2010</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>607</v>
+      </c>
+      <c r="R96" t="n">
+        <v>626</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>19952127</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19952127</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>훈핏</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ehsekqkf100@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1357-6622</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로 52 2층</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hoonfit_1</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>242</v>
+      </c>
+      <c r="R97" t="n">
+        <v>318</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1112070578</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1112070578</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>여성전용 PT 더스토리짐 부천중동점</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ndj790@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>jo1216@hanmail.net</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0507-1357-5385</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 237</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://thestorygym.co.kr/</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>422</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1527</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1949</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>36935832</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36935832</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>리온짐PT 부천신중동점</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>reongymbbc@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1359-9775</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 신흥로 256 1층, 4층</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/reongymbbc</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>2510</v>
+      </c>
+      <c r="R99" t="n">
+        <v>2850</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>1159530654</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1159530654</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>유핏 PT &amp; 폴댄스 부천점</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>cjsvnd03@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 옥산로 143-1 2층</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/u_fam_/</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>74</v>
+      </c>
+      <c r="R100" t="n">
+        <v>101</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>38432137</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38432137</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>디퍼런스짐 PT 부천중동점</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>differencegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0507-1367-6621</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 199</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://www.difference-gym.com/</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>345</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1566</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1911</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>1721487881</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1721487881</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>크리스짐</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ablegym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1391-4880</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 조마루로285번길 60</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>http://goodchrisgym.cafe24.com/</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>27</v>
+      </c>
+      <c r="R102" t="n">
+        <v>98</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>34754316</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34754316</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
